--- a/xlsx/換色紀錄表(11)-2.xlsx
+++ b/xlsx/換色紀錄表(11)-2.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_9BF17B0555DAE6BF043B541EC6D78D21E8E151BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85407478-922A-2142-8623-E0FDA20AAB69}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{796B7AB1-0E7F-2740-82F9-05565D016AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,7 +1008,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1086,19 +1086,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -1120,7 +1107,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1605,10 +1592,7 @@
     <xf numFmtId="0" fontId="30" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3057,11 +3041,11 @@
       </c>
       <c r="E2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45511</v>
+        <v>46300</v>
       </c>
       <c r="F2" s="31" t="str">
         <f ca="1">TEXT(WEEKDAY(E2,1),"aaaa")</f>
-        <v>星期三</v>
+        <v>星期一</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="33" t="s">
@@ -5022,7 +5006,9 @@
       <c r="O47" s="57"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B48" s="161"/>
+      <c r="B48" s="56">
+        <v>45240</v>
+      </c>
       <c r="C48" s="57" t="s">
         <v>20</v>
       </c>
@@ -5053,10 +5039,12 @@
       <c r="L48" s="61"/>
       <c r="M48" s="80"/>
       <c r="N48" s="57"/>
-      <c r="O48" s="162"/>
+      <c r="O48" s="161"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B49" s="161"/>
+      <c r="B49" s="56">
+        <v>45240</v>
+      </c>
       <c r="C49" s="57" t="s">
         <v>20</v>
       </c>
@@ -5085,7 +5073,7 @@
       <c r="L49" s="61"/>
       <c r="M49" s="80"/>
       <c r="N49" s="57"/>
-      <c r="O49" s="162"/>
+      <c r="O49" s="161"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B50" s="49">
@@ -9611,11 +9599,11 @@
       </c>
       <c r="G2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45511</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="97" t="str">
         <f ca="1">TEXT(WEEKDAY(每日用粉紀錄表!E2,1),"aaaa")</f>
-        <v>星期三</v>
+        <v>星期一</v>
       </c>
       <c r="I2" s="98"/>
       <c r="J2" s="98"/>
@@ -51617,17 +51605,17 @@
       </c>
     </row>
     <row r="1004" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B1004" s="163" t="s">
+      <c r="B1004" s="162" t="s">
         <v>66</v>
       </c>
-      <c r="C1004" s="164"/>
-      <c r="D1004" s="165"/>
-      <c r="E1004" s="165"/>
-      <c r="F1004" s="165"/>
-      <c r="G1004" s="165"/>
-      <c r="H1004" s="165"/>
-      <c r="I1004" s="165"/>
-      <c r="J1004" s="165"/>
+      <c r="C1004" s="163"/>
+      <c r="D1004" s="164"/>
+      <c r="E1004" s="164"/>
+      <c r="F1004" s="164"/>
+      <c r="G1004" s="164"/>
+      <c r="H1004" s="164"/>
+      <c r="I1004" s="164"/>
+      <c r="J1004" s="164"/>
     </row>
     <row r="1005" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B1005" s="129"/>
